--- a/medical_surveys_questionnaires/026_human_albumin_usage_survey--medical_surveys_questionnaires.xlsx
+++ b/medical_surveys_questionnaires/026_human_albumin_usage_survey--medical_surveys_questionnaires.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="47" customWidth="1" min="2" max="2"/>
-    <col width="47" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'medical_surveys_&amp;_questionnaires'}</t>
+          <t>medical_surveys_&amp;_questionnaires</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Medical Surveys &amp; Questionnaires'}</t>
+          <t>Medical Surveys &amp; Questionnaires</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'across_departments'}</t>
+          <t>across_departments</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Across Departments'}</t>
+          <t>Across Departments</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'clinics'}</t>
+          <t>clinics</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Clinics'}</t>
+          <t>Clinics</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'labs'}</t>
+          <t>labs</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Labs'}</t>
+          <t>Labs</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'pdf'}</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'PDF'}</t>
+          <t>PDF</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'csv'}</t>
+          <t>csv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'CSV'}</t>
+          <t>CSV</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'excel'}</t>
+          <t>excel</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Excel'}</t>
+          <t>Excel</t>
         </is>
       </c>
     </row>
